--- a/data/Test_Set_App.xlsx
+++ b/data/Test_Set_App.xlsx
@@ -2070,7 +2070,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>38-VB</t>
+          <t>38-VB_REF=388.0mgL</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3715,7 +3715,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>90-VB-Blend</t>
+          <t>90-VB-Blend_REF=669.0mgL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5360,7 +5360,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>34-VB</t>
+          <t>34-VB_REF=892.0mgL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7005,7 +7005,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>37-VT-Temp</t>
+          <t>37-VT-Temp_REF=1092.0mgL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -8650,7 +8650,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>79-VT-Merlot</t>
+          <t>79-VT-Merlot_REF=1287.0mgL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -11956,7 +11956,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>94-VB</t>
+          <t>94-VB_REF=58.0mgL</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -13601,7 +13601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>74-VB</t>
+          <t>74-VB_REF=68.8mgL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -15246,7 +15246,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>78-VT-Temp</t>
+          <t>78-VT-Temp_REF=83.9mgL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -16891,7 +16891,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-VT-Blend</t>
+          <t>25-VT-Blend_REF=97.8mgL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -18536,7 +18536,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13-VT-Temp</t>
+          <t>13-VT-Temp_REF=108.0mgL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -21842,7 +21842,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20-VT</t>
+          <t>20-VT_REF=52.7mgL</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -23487,7 +23487,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>92-VT-Merlot</t>
+          <t>92-VT-Merlot_REF=64.1mgL</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -25132,7 +25132,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>50-VB</t>
+          <t>50-VB_REF=77.1mgL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -26777,7 +26777,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>442-VT</t>
+          <t>442-VT_REF=162.7mgL</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -28422,7 +28422,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>422-VT</t>
+          <t>422-VT_REF=243.9mgL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -31728,7 +31728,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-VT-Temp</t>
+          <t>14-VT-Temp_REF=Lower</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -33375,7 +33375,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>454-VB</t>
+          <t>454-VB_REF=Lower</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -35022,7 +35022,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>535-VT</t>
+          <t>535-VT_REF=Lower</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -36669,7 +36669,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>270-VT</t>
+          <t>270-VT_REF=Higher</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -38316,7 +38316,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>463-VB</t>
+          <t>463-VB_REF=Higher</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -41624,7 +41624,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3 - VT-Blend</t>
+          <t>3 - VT-Blend_REF=Lower</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -43271,7 +43271,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26-VB-Verdejo</t>
+          <t>26-VB-Verdejo_REF=Lower</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -44918,7 +44918,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14-VT-Temp</t>
+          <t>14-VT-Temp_REF=Lower</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -46565,7 +46565,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>317-VT</t>
+          <t>317-VT_REF=Higher</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -48212,7 +48212,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>365-VT</t>
+          <t>365-VT_REF=Higher</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
